--- a/data/trans_dic/P1410-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1410-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,67</t>
+          <t>0,0; 5,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,72</t>
+          <t>0,45; 2,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,97</t>
+          <t>0,23; 2,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,35</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,44</t>
+          <t>0,32; 1,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,36</t>
+          <t>0,24; 1,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,04</t>
+          <t>0,12; 1,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>0,17; 1,72</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0,17; 1,56</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 2,07</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,9</t>
+          <t>0,14; 0,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,76</t>
+          <t>0,08; 0,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,5</t>
+          <t>0,18; 1,31</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,01</t>
+          <t>0,45; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,59</t>
+          <t>0,35; 2,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,37</t>
+          <t>0,61; 2,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,64</t>
+          <t>0,57; 2,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,07</t>
+          <t>0,5; 2,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,46</t>
+          <t>0,35; 1,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,44</t>
+          <t>0,43; 1,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,0</t>
+          <t>0,7; 1,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,3</t>
+          <t>0,32; 1,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,64</t>
+          <t>0,46; 1,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,85</t>
+          <t>1,72; 4,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,79</t>
+          <t>1,08; 3,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,24</t>
+          <t>1,0; 3,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,82</t>
+          <t>2,05; 4,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,06</t>
+          <t>1,31; 4,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,1</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,96</t>
+          <t>1,32; 3,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,98</t>
+          <t>1,53; 3,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,88</t>
+          <t>1,8; 3,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,43</t>
+          <t>0,85; 2,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,21</t>
+          <t>1,52; 3,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,09</t>
+          <t>1,97; 3,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1277,57 +1277,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 14,31</t>
+          <t>8,12; 14,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,69</t>
+          <t>3,41; 7,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,81</t>
+          <t>4,09; 8,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,21</t>
+          <t>6,77; 10,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,32</t>
+          <t>3,03; 7,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,25</t>
+          <t>3,81; 8,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,56</t>
+          <t>2,03; 5,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,7</t>
+          <t>2,26; 4,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,14</t>
+          <t>6,11; 9,69</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,26</t>
+          <t>4,13; 7,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,19</t>
+          <t>3,36; 6,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,6; 18,81</t>
+          <t>10,76; 18,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,73</t>
+          <t>6,88; 13,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 16,0</t>
+          <t>8,99; 16,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,28</t>
+          <t>7,26; 11,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,13; 12,0</t>
+          <t>6,07; 11,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 11,52</t>
+          <t>5,62; 11,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,35; 14,95</t>
+          <t>8,6; 15,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,89</t>
+          <t>4,97; 8,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 13,66</t>
+          <t>8,75; 13,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,48</t>
+          <t>7,23; 11,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,82</t>
+          <t>9,65; 14,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,88; 8,61</t>
+          <t>6,64; 9,49</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,35; 27,7</t>
+          <t>16,72; 27,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,79; 27,94</t>
+          <t>16,5; 27,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,98; 20,46</t>
+          <t>12,13; 20,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,45; 25,9</t>
+          <t>18,06; 25,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,97</t>
+          <t>12,25; 20,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,78; 22,77</t>
+          <t>14,71; 22,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,15</t>
+          <t>13,58; 22,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 21,76</t>
+          <t>16,01; 21,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,04; 21,59</t>
+          <t>14,96; 21,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,8; 23,03</t>
+          <t>16,78; 23,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,91; 20,12</t>
+          <t>14,01; 20,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,57; 21,89</t>
+          <t>17,38; 21,92</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,34</t>
+          <t>3,91; 5,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,25; 4,49</t>
+          <t>3,24; 4,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,42</t>
+          <t>3,15; 4,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,9</t>
+          <t>4,71; 6,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,46</t>
+          <t>3,15; 4,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,92</t>
+          <t>3,54; 4,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,3</t>
+          <t>3,8; 5,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,71</t>
+          <t>3,84; 4,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,66</t>
+          <t>3,71; 4,65</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 4,51</t>
+          <t>3,58; 4,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,68; 4,65</t>
+          <t>3,68; 4,68</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,11</t>
+          <t>4,46; 5,35</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>6685</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4675</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5762</t>
+          <t>0; 6163</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 7918</t>
+          <t>0; 8046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 26692</t>
+          <t>0; 21296</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4434</t>
+          <t>0; 4404</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1936; 11689</t>
+          <t>1915; 11596</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>915; 7812</t>
+          <t>923; 7928</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 13620</t>
+          <t>0; 15430</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5622</t>
+          <t>0; 6560</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2894; 12758</t>
+          <t>2874; 12777</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1916; 11122</t>
+          <t>1929; 11363</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 24089</t>
+          <t>0; 21259</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5420</t>
         </is>
       </c>
     </row>
@@ -2276,12 +2276,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>911; 7622</t>
+          <t>917; 8503</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8179</t>
+          <t>0; 6240</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 9447</t>
+          <t>0; 8317</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>866; 7694</t>
+          <t>865; 7714</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 6643</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>982; 8815</t>
+          <t>980; 9689</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>865; 10581</t>
+          <t>847; 7802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2736; 12266</t>
+          <t>1941; 11354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>972; 9896</t>
+          <t>1036; 10401</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>986; 9590</t>
+          <t>982; 8843</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2226; 14070</t>
+          <t>1766; 12780</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>10990</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5702</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2969; 13729</t>
+          <t>3038; 13767</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5957</t>
+          <t>0; 6700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1841; 13909</t>
+          <t>2157; 14090</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4242; 16354</t>
+          <t>4241; 16728</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4722; 18743</t>
+          <t>4042; 17763</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2862; 13658</t>
+          <t>3299; 14465</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1453; 7931</t>
+          <t>2171; 10133</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5785; 19094</t>
+          <t>5763; 18068</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9637; 27804</t>
+          <t>9671; 27142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4294; 17358</t>
+          <t>4302; 17180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4883; 17683</t>
+          <t>5706; 20062</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>38427</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9339; 25154</t>
+          <t>8908; 25846</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6387; 23311</t>
+          <t>6660; 23328</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6415; 20915</t>
+          <t>6447; 20857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8523; 33846</t>
+          <t>14311; 32788</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6173; 20951</t>
+          <t>6756; 20709</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2140; 12922</t>
+          <t>1120; 11041</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9388; 25708</t>
+          <t>8563; 24978</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9377; 21211</t>
+          <t>11287; 23920</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18303; 40195</t>
+          <t>18578; 39566</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10613; 29859</t>
+          <t>10401; 29334</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19077; 41556</t>
+          <t>19627; 41706</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20302; 49376</t>
+          <t>28320; 50766</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>52499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17510</t>
+          <t>19948</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66049</t>
+          <t>72447</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31651; 55350</t>
+          <t>31390; 55264</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15253; 33039</t>
+          <t>14665; 33266</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18716; 42089</t>
+          <t>19528; 42257</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36362; 62802</t>
+          <t>41190; 66833</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11936; 29559</t>
+          <t>12234; 30663</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16787; 36955</t>
+          <t>17073; 36429</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10113; 27639</t>
+          <t>10084; 27010</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11937; 25584</t>
+          <t>13684; 28976</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49443; 80182</t>
+          <t>48327; 76601</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36220; 63712</t>
+          <t>36218; 63299</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32210; 60379</t>
+          <t>32784; 60559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52691; 81287</t>
+          <t>57936; 89324</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61785</t>
+          <t>66935</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>31026; 55036</t>
+          <t>31491; 54502</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>21723; 42540</t>
+          <t>21308; 42968</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30065; 53494</t>
+          <t>30073; 53874</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27767; 45138</t>
+          <t>29509; 46963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21036; 41136</t>
+          <t>20806; 40066</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20731; 40781</t>
+          <t>19896; 41164</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31556; 56479</t>
+          <t>32484; 58601</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9319; 41819</t>
+          <t>21768; 36522</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56796; 86843</t>
+          <t>55602; 86839</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48052; 76214</t>
+          <t>47995; 76812</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69767; 105532</t>
+          <t>68732; 101586</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28063; 83938</t>
+          <t>56008; 80135</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>79879</t>
+          <t>86664</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>139185</t>
+          <t>153089</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>34326; 58144</t>
+          <t>35099; 58447</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41961; 69808</t>
+          <t>41214; 69806</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30786; 52584</t>
+          <t>31183; 51969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49347; 73241</t>
+          <t>56015; 79059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39396; 66683</t>
+          <t>40888; 68616</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>57299; 88314</t>
+          <t>57047; 88731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52453; 88646</t>
+          <t>54345; 88489</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>69074; 92570</t>
+          <t>74300; 98761</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>81783; 117423</t>
+          <t>81354; 117923</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>107153; 146850</t>
+          <t>106976; 150268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91404; 132222</t>
+          <t>92053; 132481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>124450; 155052</t>
+          <t>134628; 169722</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>176960</t>
+          <t>190965</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>147595</t>
+          <t>163028</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>324555</t>
+          <t>353993</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>128507; 175060</t>
+          <t>128162; 176137</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>111254; 153947</t>
+          <t>111168; 157690</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>105577; 150123</t>
+          <t>106988; 151519</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>132194; 204021</t>
+          <t>166361; 216189</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>105205; 150696</t>
+          <t>106550; 149062</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>126734; 174749</t>
+          <t>125933; 174392</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>134252; 187856</t>
+          <t>134684; 187085</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>124331; 172075</t>
+          <t>143315; 183498</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>244433; 310370</t>
+          <t>246647; 309740</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>248326; 314820</t>
+          <t>250073; 315456</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>255287; 322397</t>
+          <t>255624; 324470</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>279511; 363416</t>
+          <t>323764; 388032</t>
         </is>
       </c>
     </row>
